--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="O87" t="n">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="R87" t="n">
-        <v>6.261408281441764</v>
+        <v>6.706110574157798</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="O88" t="n">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="O96" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="R96" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="O97" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8373</v>
+        <v>8415</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -16745,12 +16745,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -16775,104 +16775,90 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.426914201007393</v>
+        <v>0</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16885,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16943,103 +16929,28 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O97" t="n">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.4624903844246757</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG97" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN97" t="b">
-        <v>1</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -17133,17 +17044,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17177,81 +17088,170 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17283,12 +17283,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17335,87 +17335,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17423,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -17491,98 +17472,23 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -17653,6 +17559,245 @@
         </is>
       </c>
       <c r="BC100" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -17774,7 +17919,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -17784,7 +17929,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -17836,7 +17981,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8415</v>
+        <v>8417</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -14135,13 +14135,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O80" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R80" t="n">
-        <v>1.857424617085282</v>
+        <v>1.875114375343237</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O81" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="O87" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="R87" t="n">
-        <v>6.706110574157798</v>
+        <v>6.919567674661495</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="O88" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -15656,13 +15656,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R89" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -15801,13 +15801,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O90" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="R90" t="n">
-        <v>2.388117364823933</v>
+        <v>2.529635430887574</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -15965,10 +15965,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O91" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -16929,13 +16929,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O97" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="R97" t="n">
-        <v>0.4624903844246757</v>
+        <v>0.6403713015110895</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -17088,10 +17088,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O98" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -17322,13 +17322,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17467,13 +17467,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>0.3361054069011462</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17631,10 +17631,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8417</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O87" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="R87" t="n">
-        <v>6.919567674661495</v>
+        <v>6.937355766370136</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O88" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -16929,13 +16929,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="O97" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="R97" t="n">
-        <v>0.6403713015110895</v>
+        <v>0.996133135683917</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -17088,10 +17088,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="O98" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8469</v>
+        <v>8490</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O27" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O39" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O40" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -9180,10 +9180,10 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="O51" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9336,10 +9336,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="O52" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -11396,10 +11396,10 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>421</v>
+        <v>476</v>
       </c>
       <c r="O64" t="n">
-        <v>421</v>
+        <v>476</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -11552,10 +11552,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>421</v>
+        <v>476</v>
       </c>
       <c r="O65" t="n">
-        <v>421</v>
+        <v>476</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13413,12 +13413,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -13452,81 +13452,92 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1746</v>
+        <v>729</v>
       </c>
       <c r="O76" t="n">
-        <v>1746</v>
-      </c>
-      <c r="R76" t="n">
-        <v>19.38320552925365</v>
+        <v>729</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13553,17 +13564,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -13597,22 +13608,39 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>338</v>
+        <v>729</v>
       </c>
       <c r="O77" t="n">
-        <v>338</v>
-      </c>
-      <c r="R77" t="n">
-        <v>6.012374997520785</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>729</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1530</t>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Lyme Disease</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -13620,6 +13648,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Lyme disease notifications combining confirmed and probable cases under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -13632,12 +13718,12 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1530</t>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -13645,47 +13731,47 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13712,17 +13798,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -13756,170 +13842,81 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>338</v>
+        <v>1746</v>
       </c>
       <c r="O78" t="n">
-        <v>338</v>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG78" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN78" t="b">
-        <v>1</v>
+        <v>1746</v>
+      </c>
+      <c r="R78" t="n">
+        <v>19.38320552925365</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -13951,12 +13948,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -13990,81 +13987,95 @@
         </is>
       </c>
       <c r="N79" t="n">
+        <v>338</v>
+      </c>
+      <c r="O79" t="n">
+        <v>338</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6.012374997520785</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
         <v>1</v>
       </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP79" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
-      <c r="AT79" t="n">
-        <v>0</v>
-      </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14091,17 +14102,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -14135,22 +14146,39 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>106</v>
+        <v>338</v>
       </c>
       <c r="O80" t="n">
-        <v>106</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1.875114375343237</v>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>338</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -14158,6 +14186,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN80" t="b">
+        <v>1</v>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14165,70 +14251,65 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14255,17 +14336,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -14299,175 +14380,81 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>106</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD81" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN81" t="b">
         <v>1</v>
       </c>
+      <c r="R81" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14499,12 +14486,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -14529,7 +14516,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -14538,81 +14525,100 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.875114375343237</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14639,17 +14645,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -14674,7 +14680,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -14683,81 +14689,175 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>106</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14819,7 +14919,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -14964,7 +15064,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -14973,13 +15073,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15109,7 +15209,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -15118,13 +15218,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -15224,12 +15324,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15254,104 +15354,90 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>390</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>390</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>6.937355766370136</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15378,17 +15464,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15413,179 +15499,90 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>390</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>390</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN88" t="b">
         <v>1</v>
       </c>
+      <c r="R88" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15617,12 +15614,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -15656,81 +15653,95 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>7</v>
+        <v>390</v>
       </c>
       <c r="O89" t="n">
-        <v>7</v>
+        <v>390</v>
       </c>
       <c r="R89" t="n">
-        <v>0.01356578946654432</v>
+        <v>6.937355766370136</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15757,17 +15768,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -15801,22 +15812,39 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>143</v>
+        <v>390</v>
       </c>
       <c r="O90" t="n">
-        <v>143</v>
-      </c>
-      <c r="R90" t="n">
-        <v>2.529635430887574</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>390</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -15824,6 +15852,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -15831,70 +15917,65 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15921,17 +16002,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -15965,175 +16046,81 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>143</v>
+        <v>7</v>
       </c>
       <c r="O91" t="n">
-        <v>143</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN91" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.01356578946654432</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16165,12 +16152,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16195,7 +16182,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -16204,81 +16191,100 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.529635430887574</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16305,17 +16311,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -16340,7 +16346,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -16349,81 +16355,175 @@
         </is>
       </c>
       <c r="N93" t="n">
+        <v>143</v>
+      </c>
+      <c r="O93" t="n">
+        <v>143</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
         <v>1</v>
       </c>
-      <c r="O93" t="n">
-        <v>1</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16585,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -16630,7 +16730,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -16639,13 +16739,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -16775,7 +16875,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -16890,12 +16990,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -16920,104 +17020,90 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.996133135683917</v>
+        <v>0</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17130,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17079,179 +17165,90 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>56</v>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17283,12 +17280,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17322,81 +17319,95 @@
         </is>
       </c>
       <c r="N99" t="n">
+        <v>56</v>
+      </c>
+      <c r="O99" t="n">
+        <v>56</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.996133135683917</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
         <v>1</v>
       </c>
-      <c r="O99" t="n">
-        <v>1</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP99" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
-      <c r="AT99" t="n">
-        <v>0</v>
-      </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17423,17 +17434,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -17467,22 +17478,39 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="O100" t="n">
-        <v>19</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0.3361054069011462</v>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>56</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -17490,6 +17518,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>1</v>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17497,70 +17583,65 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17587,217 +17668,526 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>19</v>
+      </c>
+      <c r="O102" t="n">
+        <v>19</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.3361054069011462</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>D109</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Lyme disease</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>莱姆病</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N101" t="n">
+      <c r="N103" t="n">
         <v>19</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O103" t="n">
         <v>19</v>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="U103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
+      <c r="V103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
-      <c r="W101" t="inlineStr">
+      <c r="W103" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>Lyme borreliose</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA101" t="inlineStr">
+      <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
+      <c r="AB103" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
+      <c r="AC103" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD101" t="inlineStr">
+      <c r="AD103" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE101" t="inlineStr">
+      <c r="AE103" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF101" t="inlineStr">
+      <c r="AF103" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG101" t="inlineStr">
+      <c r="AG103" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH101" t="inlineStr">
+      <c r="AH103" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI101" t="inlineStr">
+      <c r="AI103" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ101" t="inlineStr">
+      <c r="AJ103" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK101" t="inlineStr">
+      <c r="AK103" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AM103" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN101" t="b">
+      <c r="AN103" t="b">
         <v>1</v>
       </c>
-      <c r="AO101" t="inlineStr">
+      <c r="AO103" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP101" t="inlineStr">
+      <c r="AP103" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ101" t="inlineStr">
+      <c r="AQ103" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR101" t="inlineStr">
+      <c r="AR103" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS101" t="inlineStr">
+      <c r="AS103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
-      <c r="AT101" t="n">
+      <c r="AT103" t="n">
         <v>2</v>
       </c>
-      <c r="AU101" t="inlineStr">
+      <c r="AU103" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV101" t="inlineStr">
+      <c r="AV103" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW101" t="inlineStr">
+      <c r="AW103" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
+      <c r="AX103" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY101" t="inlineStr">
+      <c r="AY103" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
+      <c r="AZ103" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA101" t="inlineStr">
+      <c r="BA103" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB101" t="inlineStr">
+      <c r="BB103" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC101" t="inlineStr">
+      <c r="BC103" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -17919,7 +18309,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -17929,7 +18319,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -17949,7 +18339,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -17981,7 +18371,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8490</v>
+        <v>9285</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O89" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="R89" t="n">
-        <v>6.937355766370136</v>
+        <v>6.955143858078777</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O90" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="O99" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="R99" t="n">
-        <v>0.996133135683917</v>
+        <v>1.476411611817234</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="O100" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9285</v>
+        <v>9313</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="O99" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="R99" t="n">
-        <v>1.476411611817234</v>
+        <v>1.885537721115986</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="O100" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -18190,6 +18190,151 @@
       <c r="BC103" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18226,7 +18371,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18454,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -18319,7 +18464,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -18371,7 +18516,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9313</v>
+        <v>9337</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -5286,13 +5286,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O28" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R28" t="n">
-        <v>2.897489486331732</v>
+        <v>2.886387994046936</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -7502,13 +7502,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O41" t="n">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R41" t="n">
-        <v>4.351784975639996</v>
+        <v>4.3406834833552</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="O53" t="n">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="R53" t="n">
-        <v>9.691602764626827</v>
+        <v>9.636095303202847</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -11786,13 +11786,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2183</v>
+        <v>2173</v>
       </c>
       <c r="O66" t="n">
-        <v>2183</v>
+        <v>2173</v>
       </c>
       <c r="R66" t="n">
-        <v>24.23455765770947</v>
+        <v>24.12354273486151</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13842,13 +13842,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1746</v>
+        <v>1737</v>
       </c>
       <c r="O78" t="n">
-        <v>1746</v>
+        <v>1737</v>
       </c>
       <c r="R78" t="n">
-        <v>19.38320552925365</v>
+        <v>19.28329209869049</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15614,12 +15614,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -15653,95 +15653,81 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>391</v>
+        <v>1129</v>
       </c>
       <c r="O89" t="n">
-        <v>391</v>
+        <v>1129</v>
       </c>
       <c r="R89" t="n">
-        <v>6.955143858078777</v>
+        <v>12.53358478953458</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15754,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -15817,98 +15803,23 @@
       <c r="O90" t="n">
         <v>391</v>
       </c>
+      <c r="R90" t="n">
+        <v>6.955143858078777</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -16002,17 +15913,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -16046,81 +15957,170 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="O91" t="n">
-        <v>7</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0.01356578946654432</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>391</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>1</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16152,12 +16152,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16191,100 +16191,81 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>143</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
-        <v>143</v>
+        <v>7</v>
       </c>
       <c r="R92" t="n">
-        <v>2.529635430887574</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16292,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16355,103 +16336,28 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="O93" t="n">
-        <v>143</v>
+        <v>147</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2.600394463919394</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG93" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN93" t="b">
-        <v>1</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -16550,17 +16456,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16585,7 +16491,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -16594,81 +16500,175 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>147</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN94" t="b">
+        <v>1</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -16739,13 +16739,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -16884,13 +16884,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17310,104 +17310,90 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>1.885537721115986</v>
+        <v>0</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17420,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -17483,98 +17469,23 @@
       <c r="O100" t="n">
         <v>106</v>
       </c>
+      <c r="R100" t="n">
+        <v>1.885537721115986</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -17668,17 +17579,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -17712,81 +17623,170 @@
         </is>
       </c>
       <c r="N101" t="n">
+        <v>106</v>
+      </c>
+      <c r="O101" t="n">
+        <v>106</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
         <v>1</v>
       </c>
-      <c r="O101" t="n">
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
         <v>1</v>
       </c>
-      <c r="R101" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP101" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
-      <c r="AT101" t="n">
-        <v>0</v>
-      </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17818,12 +17818,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -17857,100 +17857,81 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>0.3361054069011462</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17977,7 +17958,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -18021,103 +18002,28 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="O103" t="n">
-        <v>19</v>
+        <v>42</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.7429698468341126</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN103" t="b">
-        <v>1</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -18216,123 +18122,362 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>42</v>
+      </c>
+      <c r="O104" t="n">
+        <v>42</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN104" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>D109</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Lyme disease</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
         <is>
           <t>莱姆病</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N104" t="n">
+      <c r="N105" t="n">
         <v>1</v>
       </c>
-      <c r="O104" t="n">
+      <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="R104" t="n">
+      <c r="R105" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO104" t="inlineStr">
+      <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP104" t="inlineStr">
+      <c r="AP105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR104" t="inlineStr">
+      <c r="AR105" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS104" t="inlineStr"/>
-      <c r="AT104" t="n">
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
         <v>0</v>
       </c>
-      <c r="AU104" t="inlineStr">
+      <c r="AU105" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV104" t="inlineStr">
+      <c r="AV105" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW104" t="inlineStr">
+      <c r="AW105" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
+      <c r="AX105" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY104" t="inlineStr">
+      <c r="AY105" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
+      <c r="AZ105" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA104" t="inlineStr">
+      <c r="BA105" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB104" t="inlineStr">
+      <c r="BB105" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC104" t="inlineStr">
+      <c r="BC105" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18454,7 +18599,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -18464,7 +18609,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -18516,7 +18661,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9337</v>
+        <v>10467</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -17464,13 +17464,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="O100" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="R100" t="n">
-        <v>1.885537721115986</v>
+        <v>2.116782913328324</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17623,10 +17623,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="O101" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10467</v>
+        <v>10480</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -14525,13 +14525,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="O82" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="R82" t="n">
-        <v>1.875114375343237</v>
+        <v>1.998942683148922</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -14689,10 +14689,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="O83" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -17464,13 +17464,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="O100" t="n">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="R100" t="n">
-        <v>2.116782913328324</v>
+        <v>3.664346891980123</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17623,10 +17623,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="O101" t="n">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -18002,13 +18002,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="O103" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="R103" t="n">
-        <v>0.7429698468341126</v>
+        <v>1.238283078056854</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="O104" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -18478,6 +18478,151 @@
         </is>
       </c>
       <c r="BC105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18516,7 +18661,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18599,7 +18744,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -18609,7 +18754,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
@@ -18661,7 +18806,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10480</v>
+        <v>10602</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -17464,13 +17464,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="O100" t="n">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="R100" t="n">
-        <v>3.664346891980123</v>
+        <v>5.158546595505999</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17623,10 +17623,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="O101" t="n">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -17857,13 +17857,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R102" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -18625,6 +18625,689 @@
       <c r="BC106" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18661,7 +19344,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -18744,7 +19427,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -18754,7 +19437,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -18774,7 +19457,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -18806,7 +19489,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10602</v>
+        <v>10687</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16336,13 +16336,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O93" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R93" t="n">
-        <v>2.600394463919394</v>
+        <v>2.618084222177349</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -16500,10 +16500,10 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O94" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -17464,13 +17464,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="O100" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="R100" t="n">
-        <v>5.158546595505999</v>
+        <v>5.318639420883771</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17623,10 +17623,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="O101" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -18002,13 +18002,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="O103" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="R103" t="n">
-        <v>1.238283078056854</v>
+        <v>1.804355342311416</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="O104" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -19489,7 +19489,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10687</v>
+        <v>10729</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -18801,12 +18801,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18831,12 +18831,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N108" t="n">
@@ -18853,82 +18853,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18955,7 +18941,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -19004,98 +18990,23 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN109" t="b">
-        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -19189,17 +19100,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19238,74 +19149,308 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="R110" t="n">
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO110" t="inlineStr">
+      <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP110" t="inlineStr">
+      <c r="AP111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR110" t="inlineStr">
+      <c r="AR111" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS110" t="inlineStr"/>
-      <c r="AT110" t="n">
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="n">
         <v>0</v>
       </c>
-      <c r="AU110" t="inlineStr">
+      <c r="AU111" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV110" t="inlineStr">
+      <c r="AV111" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW110" t="inlineStr">
+      <c r="AW111" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
+      <c r="AX111" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY110" t="inlineStr">
+      <c r="AY111" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
+      <c r="AZ111" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA110" t="inlineStr">
+      <c r="BA111" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB110" t="inlineStr">
+      <c r="BB111" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC110" t="inlineStr">
+      <c r="BC111" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -19427,7 +19572,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -19437,7 +19582,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -1163,6 +1163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1701,6 +1706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2089,7 +2099,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2828,10 +2838,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2984,10 +2994,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3231,6 +3241,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3769,6 +3784,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4157,7 +4177,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4896,10 +4916,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5052,10 +5072,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O27" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5286,17 +5306,22 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O28" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="R28" t="n">
-        <v>2.886387994046936</v>
+        <v>2.908590978616528</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5837,6 +5862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6225,7 +6255,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7112,10 +7142,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O39" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -7268,10 +7298,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O40" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -7502,17 +7532,22 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="O41" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="R41" t="n">
-        <v>4.3406834833552</v>
+        <v>4.373987960209587</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -8053,6 +8088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8441,7 +8481,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -9180,10 +9220,10 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="O51" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9336,10 +9376,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="O52" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -9570,17 +9610,22 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="O53" t="n">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="R53" t="n">
-        <v>9.636095303202847</v>
+        <v>9.724907241481215</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -10121,6 +10166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10509,7 +10559,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -11396,10 +11446,10 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="O64" t="n">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -11552,10 +11602,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="O65" t="n">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -11786,17 +11836,22 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2173</v>
+        <v>2189</v>
       </c>
       <c r="O66" t="n">
-        <v>2173</v>
+        <v>2189</v>
       </c>
       <c r="R66" t="n">
-        <v>24.12354273486151</v>
+        <v>24.30116661141824</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -12337,6 +12392,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12725,7 +12785,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -13452,10 +13512,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>729</v>
+        <v>802</v>
       </c>
       <c r="O76" t="n">
-        <v>729</v>
+        <v>802</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13608,10 +13668,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>729</v>
+        <v>802</v>
       </c>
       <c r="O77" t="n">
-        <v>729</v>
+        <v>802</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -13842,17 +13902,22 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1737</v>
+        <v>1751</v>
       </c>
       <c r="O78" t="n">
-        <v>1737</v>
+        <v>1751</v>
       </c>
       <c r="R78" t="n">
-        <v>19.28329209869049</v>
+        <v>19.43871299067763</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -14393,6 +14458,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14781,7 +14851,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -15614,12 +15684,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -15653,81 +15723,92 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1129</v>
+        <v>429</v>
       </c>
       <c r="O89" t="n">
-        <v>1129</v>
-      </c>
-      <c r="R89" t="n">
-        <v>12.53358478953458</v>
+        <v>429</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15754,17 +15835,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -15798,22 +15879,39 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="O90" t="n">
-        <v>391</v>
-      </c>
-      <c r="R90" t="n">
-        <v>6.955143858078777</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>429</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1530</t>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Lyme Disease</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -15821,6 +15919,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Lyme disease notifications combining confirmed and probable cases under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -15833,12 +15989,12 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1530</t>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -15846,47 +16002,47 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15913,17 +16069,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -15957,39 +16113,17 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>391</v>
+        <v>1138</v>
       </c>
       <c r="O91" t="n">
-        <v>391</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>1138</v>
+      </c>
+      <c r="R91" t="n">
+        <v>12.63349822009774</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -15997,130 +16131,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN91" t="b">
-        <v>1</v>
-      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -16152,12 +16224,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16191,81 +16263,95 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="O92" t="n">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="R92" t="n">
-        <v>0.01356578946654432</v>
+        <v>6.955143858078777</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16292,17 +16378,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -16336,22 +16422,39 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>148</v>
+        <v>391</v>
       </c>
       <c r="O93" t="n">
-        <v>148</v>
-      </c>
-      <c r="R93" t="n">
-        <v>2.618084222177349</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>391</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -16359,6 +16462,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>1</v>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -16366,70 +16527,65 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16456,17 +16612,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16500,39 +16656,17 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="O94" t="n">
-        <v>148</v>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>7</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.01356578946654432</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -16540,135 +16674,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD94" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG94" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN94" t="b">
-        <v>1</v>
-      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16700,12 +16767,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16730,7 +16797,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -16739,81 +16806,100 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.618084222177349</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16840,17 +16926,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -16875,7 +16961,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -16884,81 +16970,175 @@
         </is>
       </c>
       <c r="N96" t="n">
+        <v>148</v>
+      </c>
+      <c r="O96" t="n">
+        <v>148</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN96" t="b">
         <v>1</v>
       </c>
-      <c r="O96" t="n">
-        <v>1</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17200,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -17165,7 +17345,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -17174,13 +17354,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -17310,7 +17490,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -17425,12 +17605,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -17455,104 +17635,90 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>5.318639420883771</v>
+        <v>0</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17579,17 +17745,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -17614,179 +17780,90 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>299</v>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF101" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG101" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN101" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17818,12 +17895,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -17857,81 +17934,95 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2</v>
+        <v>339</v>
       </c>
       <c r="O102" t="n">
-        <v>2</v>
+        <v>339</v>
       </c>
       <c r="R102" t="n">
-        <v>0.003875939847584092</v>
+        <v>6.030163089229426</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17958,17 +18049,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18002,22 +18093,39 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>102</v>
+        <v>339</v>
       </c>
       <c r="O103" t="n">
-        <v>102</v>
-      </c>
-      <c r="R103" t="n">
-        <v>1.804355342311416</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>339</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -18025,6 +18133,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18032,70 +18198,65 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18122,17 +18283,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18166,39 +18327,17 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="O104" t="n">
-        <v>102</v>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>2</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -18206,135 +18345,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN104" t="b">
-        <v>1</v>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18366,12 +18438,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18396,7 +18468,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -18405,81 +18477,100 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="R105" t="n">
-        <v>0.0008168084075657662</v>
+        <v>2.122770990954607</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18506,17 +18597,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18541,7 +18632,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -18550,81 +18641,175 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>120</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18871,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -18695,13 +18880,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -18831,7 +19016,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -18946,12 +19131,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18976,12 +19161,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N109" t="n">
@@ -18998,82 +19183,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19100,17 +19271,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19135,12 +19306,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N110" t="n">
@@ -19149,165 +19320,76 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>1</v>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19339,120 +19421,921 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>18</v>
+      </c>
+      <c r="O111" t="n">
+        <v>18</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>18</v>
+      </c>
+      <c r="O112" t="n">
+        <v>18</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>D109</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Lyme disease</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>莱姆病</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N111" t="n">
+      <c r="N113" t="n">
         <v>0</v>
       </c>
-      <c r="O111" t="n">
+      <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="R111" t="n">
+      <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
+      <c r="S113" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO111" t="inlineStr">
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP111" t="inlineStr">
+      <c r="AP113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR111" t="inlineStr">
+      <c r="AR113" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS111" t="inlineStr"/>
-      <c r="AT111" t="n">
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
         <v>0</v>
       </c>
-      <c r="AU111" t="inlineStr">
+      <c r="AU113" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV111" t="inlineStr">
+      <c r="AV113" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW111" t="inlineStr">
+      <c r="AW113" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
+      <c r="AX113" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY111" t="inlineStr">
+      <c r="AY113" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
+      <c r="AZ113" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA111" t="inlineStr">
+      <c r="BA113" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB111" t="inlineStr">
+      <c r="BB113" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC111" t="inlineStr">
+      <c r="BC113" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>11</v>
+      </c>
+      <c r="O114" t="n">
+        <v>11</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>11</v>
+      </c>
+      <c r="O115" t="n">
+        <v>11</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN115" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19572,7 +20455,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -19582,7 +20465,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -19602,7 +20485,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -19634,7 +20517,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10729</v>
+        <v>11411</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -17934,13 +17934,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O102" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R102" t="n">
-        <v>6.030163089229426</v>
+        <v>6.047951180938067</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O103" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -19460,13 +19460,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="O111" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="R111" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.9783450439752756</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -19619,10 +19619,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="O112" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11411</v>
+        <v>11449</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -16806,13 +16806,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O95" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R95" t="n">
-        <v>2.618084222177349</v>
+        <v>2.600394463919394</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -16970,10 +16970,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O96" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -17934,13 +17934,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O102" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="R102" t="n">
-        <v>6.047951180938067</v>
+        <v>6.101315456063992</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O103" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -18477,13 +18477,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O105" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R105" t="n">
-        <v>2.122770990954607</v>
+        <v>2.105081232696652</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -18641,10 +18641,10 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O106" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -19460,13 +19460,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="O111" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="R111" t="n">
-        <v>0.9783450439752756</v>
+        <v>1.262954511313538</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -19619,10 +19619,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="O112" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -20003,13 +20003,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="O114" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="R114" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.6191415390284272</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -20167,10 +20167,10 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="O115" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -20336,6 +20336,151 @@
       <c r="BC115" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20372,7 +20517,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20455,7 +20600,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -20465,7 +20610,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -20517,7 +20662,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11449</v>
+        <v>11490</v>
       </c>
     </row>
     <row r="16">
